--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_start_end.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_start_end.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680FC967-B7BC-4646-BC8C-0291133FB22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A89784-2923-4DF3-8CFD-D97DAE41C735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{14E777A4-5F58-47BE-8B5E-2F3A2EFF9B18}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="6">
   <si>
     <t>Date_AKDT</t>
   </si>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A47BB3D-3039-4721-AE08-9955970D5607}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
@@ -815,6 +815,538 @@
         <v>5</v>
       </c>
     </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>531</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.3591550925925926</v>
+      </c>
+      <c r="D28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>531</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.39045138888888886</v>
+      </c>
+      <c r="D29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>532</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.42435185185185187</v>
+      </c>
+      <c r="D30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>532</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.45504629629629628</v>
+      </c>
+      <c r="D31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>533</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.50728009259259255</v>
+      </c>
+      <c r="D32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>533</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.52915509259259264</v>
+      </c>
+      <c r="D33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>534</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.62760416666666663</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>534</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.63582175925925921</v>
+      </c>
+      <c r="D35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>535</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.64042824074074078</v>
+      </c>
+      <c r="D36" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>535</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.66607638888888887</v>
+      </c>
+      <c r="D37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>536</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.67184027777777777</v>
+      </c>
+      <c r="D38" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>536</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.70594907407407403</v>
+      </c>
+      <c r="D39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>537</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.79642361111111115</v>
+      </c>
+      <c r="D40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>537</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46241</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.83608796296296295</v>
+      </c>
+      <c r="D41" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>538</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.35037037037037039</v>
+      </c>
+      <c r="D42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>538</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.3976736111111111</v>
+      </c>
+      <c r="D43" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>539</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.40555555555555556</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>539</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.41740740740740739</v>
+      </c>
+      <c r="D45" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>540</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.46487268518518521</v>
+      </c>
+      <c r="D46" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>540</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.50079861111111112</v>
+      </c>
+      <c r="D47" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>541</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0.54954861111111108</v>
+      </c>
+      <c r="D48" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>541</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.56899305555555557</v>
+      </c>
+      <c r="D49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>542</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0.56930555555555551</v>
+      </c>
+      <c r="D50" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>542</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.60928240740740736</v>
+      </c>
+      <c r="D51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>543</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0.627349537037037</v>
+      </c>
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>543</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46242</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0.65515046296296298</v>
+      </c>
+      <c r="D53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>544</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0.69802083333333331</v>
+      </c>
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>544</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0.73299768518518515</v>
+      </c>
+      <c r="D55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>545</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0.31443287037037038</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>545</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C57" s="2">
+        <v>0.38197916666666665</v>
+      </c>
+      <c r="D57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>546</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0.40307870370370369</v>
+      </c>
+      <c r="D58" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>546</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0.46629629629629632</v>
+      </c>
+      <c r="D59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>547</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D60" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>547</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0.65820601851851857</v>
+      </c>
+      <c r="D61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>548</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C62" s="2">
+        <v>0.66459490740740745</v>
+      </c>
+      <c r="D62" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>548</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C63" s="2">
+        <v>0.70901620370370366</v>
+      </c>
+      <c r="D63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>549</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C64" s="2">
+        <v>0.75555555555555554</v>
+      </c>
+      <c r="D64" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>549</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46243</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0.80290509259259257</v>
+      </c>
+      <c r="D65" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_start_end.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_start_end.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A89784-2923-4DF3-8CFD-D97DAE41C735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59D936E-76B9-4D89-9680-2A1235F4EBAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{14E777A4-5F58-47BE-8B5E-2F3A2EFF9B18}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="6">
   <si>
     <t>Date_AKDT</t>
   </si>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A47BB3D-3039-4721-AE08-9955970D5607}">
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.28515625" customWidth="1"/>
@@ -1347,6 +1347,50 @@
         <v>5</v>
       </c>
     </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>550</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46247</v>
+      </c>
+      <c r="D66" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>550</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46247</v>
+      </c>
+      <c r="D67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>551</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46247</v>
+      </c>
+      <c r="D68" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>551</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46247</v>
+      </c>
+      <c r="D69" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
